--- a/reports/Debug-purgatory-20260104/Month to Date (Prior Year)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/Month to Date (Prior Year)_Revenue.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="63">
   <si>
     <t>DepartmentTitle</t>
   </si>
@@ -64,24 +64,60 @@
     <t>Village Market Deli</t>
   </si>
   <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Purgatory</t>
+  </si>
+  <si>
+    <t>Housekeeping</t>
+  </si>
+  <si>
+    <t>Resort Services G&amp;A</t>
+  </si>
+  <si>
+    <t>Accounting/Mgmt Services</t>
+  </si>
+  <si>
     <t>Guest Services</t>
   </si>
   <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Engineering</t>
+  </si>
+  <si>
     <t>Grounds Maintenance</t>
   </si>
   <si>
+    <t>Transportation</t>
+  </si>
+  <si>
+    <t>Commercial Tenants</t>
+  </si>
+  <si>
+    <t>General Administration</t>
+  </si>
+  <si>
     <t>account</t>
   </si>
   <si>
+    <t>T105</t>
+  </si>
+  <si>
+    <t>T101</t>
+  </si>
+  <si>
+    <t>T100</t>
+  </si>
+  <si>
+    <t>T103</t>
+  </si>
+  <si>
     <t>T104</t>
   </si>
   <si>
-    <t>T105</t>
-  </si>
-  <si>
-    <t>T100</t>
-  </si>
-  <si>
     <t>department</t>
   </si>
   <si>
@@ -112,10 +148,10 @@
     <t>D5201</t>
   </si>
   <si>
-    <t xml:space="preserve">D5202                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">D5205                    </t>
+    <t>D5202</t>
+  </si>
+  <si>
+    <t>D5205</t>
   </si>
   <si>
     <t>D5206</t>
@@ -130,10 +166,40 @@
     <t>D5209</t>
   </si>
   <si>
-    <t xml:space="preserve">D6720                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve">D6780                    </t>
+    <t>D5810</t>
+  </si>
+  <si>
+    <t>D6212</t>
+  </si>
+  <si>
+    <t>D6215</t>
+  </si>
+  <si>
+    <t>D6700</t>
+  </si>
+  <si>
+    <t>D6710</t>
+  </si>
+  <si>
+    <t>D6720</t>
+  </si>
+  <si>
+    <t>D6730</t>
+  </si>
+  <si>
+    <t>D6750</t>
+  </si>
+  <si>
+    <t>D6780</t>
+  </si>
+  <si>
+    <t>D6790</t>
+  </si>
+  <si>
+    <t>D6800</t>
+  </si>
+  <si>
+    <t>D8010</t>
   </si>
   <si>
     <t>revenue</t>
@@ -499,13 +565,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -513,13 +579,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -527,13 +593,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D2" s="2">
-        <v>311.1200</v>
+        <v>13137.00</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -541,13 +607,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D3" s="2">
-        <v>13137.0000</v>
+        <v>331510.52</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -555,205 +621,353 @@
         <v>1</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D4" s="2">
-        <v>906468.7030</v>
+        <v>906338.71</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>32</v>
+      </c>
       <c r="C5" s="2" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D5" s="2">
-        <v>228706.7100</v>
+        <v>10905.00</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>1</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="C6" s="2" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D6" s="2">
-        <v>6540.0000</v>
+        <v>311.12</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" s="2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2">
-        <v>163578.3300</v>
+        <v>228427.71</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" s="2" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D8" s="2">
-        <v>15176.7000</v>
+        <v>6540.00</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2">
-        <v>61369.9100</v>
+        <v>169548.33</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D10" s="2">
-        <v>24335.2600</v>
+        <v>15176.70</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D11" s="2">
-        <v>26159.9000</v>
+        <v>61369.91</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D12" s="2">
-        <v>33101.2900</v>
+        <v>24438.96</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D13" s="2">
-        <v>52144.7800</v>
+        <v>26159.90</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D14" s="2">
-        <v>7389.2000</v>
+        <v>33101.29</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D15" s="2">
-        <v>3500.0000</v>
+        <v>52086.36</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D16" s="2">
-        <v>29096.3600</v>
+        <v>7389.20</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D17" s="2">
-        <v>80495.2900</v>
+        <v>3501.44</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D18" s="2">
-        <v>19680.7700</v>
+        <v>29096.36</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D19" s="2">
-        <v>8310.0000</v>
+        <v>80495.29</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2">
-        <v>160.0000</v>
+        <v>19416.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D21" s="2">
+        <v>12000.00</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="2">
+        <v>290126.88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D23" s="2">
+        <v>4140.00</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="2">
+        <v>2503.80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D25" s="2">
+        <v>6133.36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="2">
+        <v>2340.00</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
+      <c r="A27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="2">
+        <v>843.84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
+      <c r="A28" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="2">
+        <v>2661.64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
+      <c r="A29" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D29" s="2">
+        <v>1952.88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="2">
+        <v>3033.04</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D31" s="2">
+        <v>17508.17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
+      <c r="A32" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D32" s="2">
+        <v>6420.69</v>
       </c>
     </row>
   </sheetData>
